--- a/data_lake/macro/South Korea/Export Comp.xlsx
+++ b/data_lake/macro/South Korea/Export Comp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/macro/South Korea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F2B06D-573D-4590-9B4C-4F53825B2F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F1E5E-A891-A142-936A-8B995B8AE068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EXPORT" sheetId="1" r:id="rId1"/>
@@ -1787,19 +1787,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I462"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.26953125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.36328125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="11.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>32143</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>59623</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>32174</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>49141</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>32203</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>26297</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>32234</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>35484</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>32264</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>86699</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>32295</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>150719</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>32325</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>78449</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>32356</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>290411</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>32387</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>221079</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>32417</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>120275</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>32448</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>389322</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>32478</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>280317</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>32509</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>76239</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>32540</v>
       </c>
@@ -2150,7 +2150,7 @@
         <v>51908</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>32568</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>55917</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>32599</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>81283</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>32629</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>63151</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>32660</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>170255</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>32690</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>138411</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>32721</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>76307</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>32752</v>
       </c>
@@ -2311,7 +2311,7 @@
         <v>198291</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>32782</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>242131</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>32813</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>294762</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>32843</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>362535</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>32874</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>14984</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>32905</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>169112</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>32933</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>113475</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>32964</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>168061</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>32994</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>94004</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>33025</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>291224</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>33055</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>229123</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>33086</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>123342</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>33117</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>220021</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>33147</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>400407</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>33178</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>374046</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>33208</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>630929</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>33239</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>48004</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>33270</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>120788</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>33298</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>273791</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>33329</v>
       </c>
@@ -2748,7 +2748,7 @@
         <v>247655</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>33359</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>346948</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>33390</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>558468</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>33420</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>63792</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>33451</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>314981</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>33482</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>153150</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>33512</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>515795</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>33543</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>644087</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>33573</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>869510</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>33604</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>104285</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>33635</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>222846</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>33664</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>461104</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>33695</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>275759</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>33725</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>329327</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>33756</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>526905</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>33786</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>144853</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>33817</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>317602</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>33848</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>380231</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>33878</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>579235</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>33909</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>595203</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>33939</v>
       </c>
@@ -3208,7 +3208,7 @@
         <v>204667</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>33970</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>149363</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>34001</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>137754</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>34029</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>248598</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>34060</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>200845</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>34090</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>421865</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>34121</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>501299</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>34151</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>120235</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>34182</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>327194</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>34213</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>314152</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>34243</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>844961</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>34274</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>314840</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>34304</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>539626</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>34335</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>201385</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>34366</v>
       </c>
@@ -3530,7 +3530,7 @@
         <v>394041</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>34394</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>292551</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>34425</v>
       </c>
@@ -3576,7 +3576,7 @@
         <v>458362</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>34455</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>513505</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>34486</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>463171</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>34516</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>92525</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>34547</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>128759</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>34578</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>531657</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>34608</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>537006</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>34639</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>549098</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>34669</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>894826</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>34700</v>
       </c>
@@ -3783,7 +3783,7 @@
         <v>232588</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>34731</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>376676</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>34759</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>243743</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>34790</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>411632</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>34820</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>461585</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>34851</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>493257</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>34881</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>319045</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>34912</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>601596</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>34943</v>
       </c>
@@ -3967,7 +3967,7 @@
         <v>721672</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>34973</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>548740</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>35004</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>591472</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>35034</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>667340</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>35065</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>222417</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>35096</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>399703</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>35125</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>932302</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>35156</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>327965</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>35186</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>796932</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>35217</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>963792</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>35247</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>406197</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>35278</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>456193</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>35309</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>305466</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>35339</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>1035352</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>35370</v>
       </c>
@@ -4289,7 +4289,7 @@
         <v>566796</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="3">
         <v>35400</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>794629</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="3">
         <v>35431</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>143523</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>35462</v>
       </c>
@@ -4358,7 +4358,7 @@
         <v>305168</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>35490</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>399367</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>35521</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>495521</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>35551</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>464967</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>35582</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>798433</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>35612</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>404262</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>35643</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>459914</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>35674</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>524042</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>35704</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>721831</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>35735</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>834710</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>35765</v>
       </c>
@@ -4588,7 +4588,7 @@
         <v>1100045</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>35796</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>208024</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>35827</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>440392</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>35855</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>632731</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>35886</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>712362</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>35916</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>506441</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>35947</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>1414077</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>35977</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>223342</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>36008</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>674998</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>36039</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>587104</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>36069</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>482484</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>36100</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>1033843</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>36130</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>1224609</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>36161</v>
       </c>
@@ -4887,7 +4887,7 @@
         <v>236545</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>36192</v>
       </c>
@@ -4910,7 +4910,7 @@
         <v>376398</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>36220</v>
       </c>
@@ -4933,7 +4933,7 @@
         <v>680363</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>36251</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>715359</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>36281</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>529837</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>36312</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>791379</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>36342</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>341204</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>36373</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>454991</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>36404</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>471103</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>36434</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>438592</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>36465</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>1070939</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>36495</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>1548064</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>36526</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>333751</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
         <v>36557</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>815274</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>36586</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>695119</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>36617</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>791107</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>36647</v>
       </c>
@@ -5255,7 +5255,7 @@
         <v>593379</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>36678</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>812737</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>36708</v>
       </c>
@@ -5301,7 +5301,7 @@
         <v>478910</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>36739</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>622529</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>36770</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>580398</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="3">
         <v>36800</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>655338</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
         <v>36831</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>854615</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>36861</v>
       </c>
@@ -5416,7 +5416,7 @@
         <v>1186898</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>36892</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>1141268</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>36923</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>1114549</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>36951</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>966139</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>36982</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>628342</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>37012</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>1097904</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>37043</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>838226</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>37073</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>607087</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>37104</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>657492</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>37135</v>
       </c>
@@ -5623,7 +5623,7 @@
         <v>509235</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>37165</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>817152</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>37196</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>571718</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="3">
         <v>37226</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>959692</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>37257</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>585509</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
         <v>37288</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>889746</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>37316</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>870115</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>37347</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>699527</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>37377</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>1137955</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>37408</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>935211</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>37438</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>575986</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="3">
         <v>37469</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>939085</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="3">
         <v>37500</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>1009834</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="3">
         <v>37530</v>
       </c>
@@ -5922,7 +5922,7 @@
         <v>605071</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="3">
         <v>37561</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>1114781</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="3">
         <v>37591</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>1504378</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="3">
         <v>37622</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>1126668</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="3">
         <v>37653</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>624314</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="3">
         <v>37681</v>
       </c>
@@ -6037,7 +6037,7 @@
         <v>983911</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="3">
         <v>37712</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>1288462</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="3">
         <v>37742</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>844006</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="3">
         <v>37773</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>1392758</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="3">
         <v>37803</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>791801</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="3">
         <v>37834</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>999095</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>37865</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>1034549</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="3">
         <v>37895</v>
       </c>
@@ -6198,7 +6198,7 @@
         <v>535818</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="3">
         <v>37926</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>716691</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="3">
         <v>37956</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>995763</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="3">
         <v>37987</v>
       </c>
@@ -6267,7 +6267,7 @@
         <v>2619999</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" s="3">
         <v>38018</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>955072</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>38047</v>
       </c>
@@ -6313,7 +6313,7 @@
         <v>827356</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="3">
         <v>38078</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>1423035</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="3">
         <v>38108</v>
       </c>
@@ -6359,7 +6359,7 @@
         <v>805195</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="3">
         <v>38139</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>1943140</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="3">
         <v>38169</v>
       </c>
@@ -6405,7 +6405,7 @@
         <v>1089690</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="3">
         <v>38200</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>1028026</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="3">
         <v>38231</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>923720</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="3">
         <v>38261</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>1118353</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" s="3">
         <v>38292</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>1299867</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" s="3">
         <v>38322</v>
       </c>
@@ -6520,7 +6520,7 @@
         <v>1623210</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" s="3">
         <v>38353</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>1988552</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" s="3">
         <v>38384</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>1954324</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" s="3">
         <v>38412</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>972090</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" s="3">
         <v>38443</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>1476525</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" s="3">
         <v>38473</v>
       </c>
@@ -6635,7 +6635,7 @@
         <v>1546253</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" s="3">
         <v>38504</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>1370088</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" s="3">
         <v>38534</v>
       </c>
@@ -6681,7 +6681,7 @@
         <v>1064691</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" s="3">
         <v>38565</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>1314062</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" s="3">
         <v>38596</v>
       </c>
@@ -6727,7 +6727,7 @@
         <v>1433298</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" s="3">
         <v>38626</v>
       </c>
@@ -6750,7 +6750,7 @@
         <v>1664109</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" s="3">
         <v>38657</v>
       </c>
@@ -6773,7 +6773,7 @@
         <v>1177938</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" s="3">
         <v>38687</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>1765042</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" s="3">
         <v>38718</v>
       </c>
@@ -6819,7 +6819,7 @@
         <v>1272647</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" s="3">
         <v>38749</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>1956599</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" s="3">
         <v>38777</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>1631254</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" s="3">
         <v>38808</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>2065832</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" s="3">
         <v>38838</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>2407790</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" s="3">
         <v>38869</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>2038044</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
         <v>38899</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>1658831</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="3">
         <v>38930</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>1466608</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="3">
         <v>38961</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>1129218</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" s="3">
         <v>38991</v>
       </c>
@@ -7026,7 +7026,7 @@
         <v>2193001</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
         <v>39022</v>
       </c>
@@ -7049,7 +7049,7 @@
         <v>2245616</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" s="3">
         <v>39052</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>2057339</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" s="3">
         <v>39083</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>2323150</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="3">
         <v>39114</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>1805519</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" s="3">
         <v>39142</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>2213392</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" s="3">
         <v>39173</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>2318972</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" s="3">
         <v>39203</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>3143464</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="3">
         <v>39234</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>3702067</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="3">
         <v>39264</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>1262997</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="3">
         <v>39295</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>1572062</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" s="3">
         <v>39326</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>1643865</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" s="3">
         <v>39356</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>1915371</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" s="3">
         <v>39387</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>2834164</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="3">
         <v>39417</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>3041240</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="3">
         <v>39448</v>
       </c>
@@ -7371,7 +7371,7 @@
         <v>2214968</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="3">
         <v>39479</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>2871976</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="3">
         <v>39508</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>2551632</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="3">
         <v>39539</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>3445840</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>39569</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>4808050</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="3">
         <v>39600</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>2994621</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>39630</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>3561253</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="3">
         <v>39661</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>3881970</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="3">
         <v>39692</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>3749291</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="3">
         <v>39722</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>4209552</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="3">
         <v>39753</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>3746586</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="3">
         <v>39783</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>5120775</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="3">
         <v>39814</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>2467320</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="3">
         <v>39845</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>4310770</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="3">
         <v>39873</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>4017652</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="3">
         <v>39904</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>4731761</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="3">
         <v>39934</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>3785160</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="3">
         <v>39965</v>
       </c>
@@ -7762,7 +7762,7 @@
         <v>4811535</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="3">
         <v>39995</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>3303578</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="3">
         <v>40026</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>2674798</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="3">
         <v>40057</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>3495642</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="3">
         <v>40087</v>
       </c>
@@ -7854,7 +7854,7 @@
         <v>3955634</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="3">
         <v>40118</v>
       </c>
@@ -7877,7 +7877,7 @@
         <v>3518075</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="3">
         <v>40148</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>4056067</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="3">
         <v>40179</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>1891499</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="3">
         <v>40210</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>4776155</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="3">
         <v>40238</v>
       </c>
@@ -7969,7 +7969,7 @@
         <v>3226688</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="3">
         <v>40269</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>4119675</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="3">
         <v>40299</v>
       </c>
@@ -8015,7 +8015,7 @@
         <v>4211190</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="3">
         <v>40330</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>6342845</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="3">
         <v>40360</v>
       </c>
@@ -8061,7 +8061,7 @@
         <v>4355044</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" s="3">
         <v>40391</v>
       </c>
@@ -8084,7 +8084,7 @@
         <v>2391046</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" s="3">
         <v>40422</v>
       </c>
@@ -8107,7 +8107,7 @@
         <v>4661464</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" s="3">
         <v>40452</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>4877122</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" s="3">
         <v>40483</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>3432539</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" s="3">
         <v>40513</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>4826371</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" s="3">
         <v>40544</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>6740549</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" s="3">
         <v>40575</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>4185406</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" s="3">
         <v>40603</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>5451596</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" s="3">
         <v>40634</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>6264944</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" s="3">
         <v>40664</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>5180005</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" s="3">
         <v>40695</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>4104863</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" s="3">
         <v>40725</v>
       </c>
@@ -8337,7 +8337,7 @@
         <v>4937620</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" s="3">
         <v>40756</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>4290058</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" s="3">
         <v>40787</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>3145934</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" s="3">
         <v>40817</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>4324623</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" s="3">
         <v>40848</v>
       </c>
@@ -8429,7 +8429,7 @@
         <v>3592105</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="3">
         <v>40878</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>4370031</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="3">
         <v>40909</v>
       </c>
@@ -8475,7 +8475,7 @@
         <v>3834547</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="3">
         <v>40940</v>
       </c>
@@ -8498,7 +8498,7 @@
         <v>4515665</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="3">
         <v>40969</v>
       </c>
@@ -8521,7 +8521,7 @@
         <v>3870192</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" s="3">
         <v>41000</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>4797261</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" s="3">
         <v>41030</v>
       </c>
@@ -8567,7 +8567,7 @@
         <v>4181192</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" s="3">
         <v>41061</v>
       </c>
@@ -8590,7 +8590,7 @@
         <v>4266806</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" s="3">
         <v>41091</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>2141340</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" s="3">
         <v>41122</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>2802327</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" s="3">
         <v>41153</v>
       </c>
@@ -8659,7 +8659,7 @@
         <v>1632799</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" s="3">
         <v>41183</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>3060088</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" s="3">
         <v>41214</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>1943230</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" s="3">
         <v>41244</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>2707122</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" s="3">
         <v>41275</v>
       </c>
@@ -8751,7 +8751,7 @@
         <v>2963179</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" s="3">
         <v>41306</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>2660235</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" s="3">
         <v>41334</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>3294193</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" s="3">
         <v>41365</v>
       </c>
@@ -8820,7 +8820,7 @@
         <v>2617943</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" s="3">
         <v>41395</v>
       </c>
@@ -8843,7 +8843,7 @@
         <v>2748991</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" s="3">
         <v>41426</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>4573945</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" s="3">
         <v>41456</v>
       </c>
@@ -8889,7 +8889,7 @@
         <v>2526793</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" s="3">
         <v>41487</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>3442648</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" s="3">
         <v>41518</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>2665207</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" s="3">
         <v>41548</v>
       </c>
@@ -8958,7 +8958,7 @@
         <v>3190407</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" s="3">
         <v>41579</v>
       </c>
@@ -8981,7 +8981,7 @@
         <v>2533519</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" s="3">
         <v>41609</v>
       </c>
@@ -9004,7 +9004,7 @@
         <v>3950833</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" s="3">
         <v>41640</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>2796382</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" s="3">
         <v>41671</v>
       </c>
@@ -9050,7 +9050,7 @@
         <v>2406671</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" s="3">
         <v>41699</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>3269895</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" s="3">
         <v>41730</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>3109137</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" s="3">
         <v>41760</v>
       </c>
@@ -9119,7 +9119,7 @@
         <v>3485098</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" s="3">
         <v>41791</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>4900115</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" s="3">
         <v>41821</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>2210177</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" s="3">
         <v>41852</v>
       </c>
@@ -9188,7 +9188,7 @@
         <v>3577738</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" s="3">
         <v>41883</v>
       </c>
@@ -9211,7 +9211,7 @@
         <v>3299587</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" s="3">
         <v>41913</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>4528774</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" s="3">
         <v>41944</v>
       </c>
@@ -9257,7 +9257,7 @@
         <v>2453142</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" s="3">
         <v>41974</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>3848835</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" s="3">
         <v>42005</v>
       </c>
@@ -9303,7 +9303,7 @@
         <v>4381561</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" s="3">
         <v>42036</v>
       </c>
@@ -9326,7 +9326,7 @@
         <v>5306189</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" s="3">
         <v>42064</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>3629277</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" s="3">
         <v>42095</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>2830996</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" s="3">
         <v>42125</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>2292572</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" s="3">
         <v>42156</v>
       </c>
@@ -9418,7 +9418,7 @@
         <v>3951301</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" s="3">
         <v>42186</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>3456399</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" s="3">
         <v>42217</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>1711822</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" s="3">
         <v>42248</v>
       </c>
@@ -9487,7 +9487,7 @@
         <v>2598991</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" s="3">
         <v>42278</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>1717869</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" s="3">
         <v>42309</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>5636407</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" s="3">
         <v>42339</v>
       </c>
@@ -9556,7 +9556,7 @@
         <v>2593213</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" s="3">
         <v>42370</v>
       </c>
@@ -9579,7 +9579,7 @@
         <v>2666924</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" s="3">
         <v>42401</v>
       </c>
@@ -9602,7 +9602,7 @@
         <v>2687780</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" s="3">
         <v>42430</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>2593137</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" s="3">
         <v>42461</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>3513993</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" s="3">
         <v>42491</v>
       </c>
@@ -9671,7 +9671,7 @@
         <v>1914026</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" s="3">
         <v>42522</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>5148711</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" s="3">
         <v>42552</v>
       </c>
@@ -9717,7 +9717,7 @@
         <v>1976814</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" s="3">
         <v>42583</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>3242800</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" s="3">
         <v>42614</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>2238350</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" s="3">
         <v>42644</v>
       </c>
@@ -9786,7 +9786,7 @@
         <v>2554211</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" s="3">
         <v>42675</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>3515609</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" s="3">
         <v>42705</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>2215753</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" s="3">
         <v>42736</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>2187573</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" s="3">
         <v>42767</v>
       </c>
@@ -9878,7 +9878,7 @@
         <v>1897742</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" s="3">
         <v>42795</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>2890099</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" s="3">
         <v>42826</v>
       </c>
@@ -9924,7 +9924,7 @@
         <v>7123485</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" s="3">
         <v>42856</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>2441600</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" s="3">
         <v>42887</v>
       </c>
@@ -9970,7 +9970,7 @@
         <v>7371994</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" s="3">
         <v>42917</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>6090240</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" s="3">
         <v>42948</v>
       </c>
@@ -10016,7 +10016,7 @@
         <v>2426802</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" s="3">
         <v>42979</v>
       </c>
@@ -10039,7 +10039,7 @@
         <v>3124204</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" s="3">
         <v>43009</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>3290540</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" s="3">
         <v>43040</v>
       </c>
@@ -10085,7 +10085,7 @@
         <v>803786</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" s="3">
         <v>43070</v>
       </c>
@@ -10108,7 +10108,7 @@
         <v>2533740</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" s="3">
         <v>43101</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>2445002</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" s="3">
         <v>43132</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>2461981</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" s="3">
         <v>43160</v>
       </c>
@@ -10177,7 +10177,7 @@
         <v>1992904</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" s="3">
         <v>43191</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>1776928</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" s="3">
         <v>43221</v>
       </c>
@@ -10223,7 +10223,7 @@
         <v>821711</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" s="3">
         <v>43252</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>1314885</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" s="3">
         <v>43282</v>
       </c>
@@ -10269,7 +10269,7 @@
         <v>1628902</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" s="3">
         <v>43313</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>672014</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" s="3">
         <v>43344</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>1390914</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" s="3">
         <v>43374</v>
       </c>
@@ -10338,7 +10338,7 @@
         <v>1484909</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" s="3">
         <v>43405</v>
       </c>
@@ -10361,7 +10361,7 @@
         <v>2078071</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373" s="3">
         <v>43435</v>
       </c>
@@ -10384,7 +10384,7 @@
         <v>3207123</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374" s="3">
         <v>43466</v>
       </c>
@@ -10407,7 +10407,7 @@
         <v>1776981</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375" s="3">
         <v>43497</v>
       </c>
@@ -10430,7 +10430,7 @@
         <v>1324398</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376" s="3">
         <v>43525</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>2098984</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" s="3">
         <v>43556</v>
       </c>
@@ -10476,7 +10476,7 @@
         <v>2732736</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" s="3">
         <v>43586</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>1185374</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" s="3">
         <v>43617</v>
       </c>
@@ -10522,7 +10522,7 @@
         <v>1923368</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380" s="3">
         <v>43647</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>1513124</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381" s="3">
         <v>43678</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>1803195</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A382" s="3">
         <v>43709</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>1803954</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383" s="3">
         <v>43739</v>
       </c>
@@ -10614,7 +10614,7 @@
         <v>1856935</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A384" s="3">
         <v>43770</v>
       </c>
@@ -10637,7 +10637,7 @@
         <v>789098</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385" s="3">
         <v>43800</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>1350835</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386" s="3">
         <v>43831</v>
       </c>
@@ -10683,7 +10683,7 @@
         <v>2825495</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387" s="3">
         <v>43862</v>
       </c>
@@ -10706,7 +10706,7 @@
         <v>1445358</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388" s="3">
         <v>43891</v>
       </c>
@@ -10729,7 +10729,7 @@
         <v>1440070</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389" s="3">
         <v>43922</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>1067837</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A390" s="3">
         <v>43952</v>
       </c>
@@ -10775,7 +10775,7 @@
         <v>1608433</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A391" s="3">
         <v>43983</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>1380315</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A392" s="3">
         <v>44013</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>1787501</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A393" s="3">
         <v>44044</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>1174615</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A394" s="3">
         <v>44075</v>
       </c>
@@ -10867,7 +10867,7 @@
         <v>1739152</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A395" s="3">
         <v>44105</v>
       </c>
@@ -10890,7 +10890,7 @@
         <v>1449398</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A396" s="3">
         <v>44136</v>
       </c>
@@ -10913,7 +10913,7 @@
         <v>1044614</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A397" s="3">
         <v>44166</v>
       </c>
@@ -10936,7 +10936,7 @@
         <v>2786045</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A398" s="3">
         <v>44197</v>
       </c>
@@ -10959,7 +10959,7 @@
         <v>3486960</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A399" s="3">
         <v>44228</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>1497916</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A400" s="3">
         <v>44256</v>
       </c>
@@ -11005,7 +11005,7 @@
         <v>2339309</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A401" s="3">
         <v>44287</v>
       </c>
@@ -11028,7 +11028,7 @@
         <v>1221888</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A402" s="3">
         <v>44317</v>
       </c>
@@ -11051,7 +11051,7 @@
         <v>1362921</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A403" s="3">
         <v>44348</v>
       </c>
@@ -11074,7 +11074,7 @@
         <v>1950990</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A404" s="3">
         <v>44378</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>1969324</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A405" s="3">
         <v>44409</v>
       </c>
@@ -11120,7 +11120,7 @@
         <v>1631185</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A406" s="3">
         <v>44440</v>
       </c>
@@ -11143,7 +11143,7 @@
         <v>1036496</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A407" s="3">
         <v>44470</v>
       </c>
@@ -11166,7 +11166,7 @@
         <v>1542651</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A408" s="3">
         <v>44501</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>3527434</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A409" s="3">
         <v>44531</v>
       </c>
@@ -11212,7 +11212,7 @@
         <v>1420431</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A410" s="3">
         <v>44562</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>770171</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A411" s="3">
         <v>44593</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>1733796</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A412" s="3">
         <v>44621</v>
       </c>
@@ -11281,7 +11281,7 @@
         <v>1503874</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A413" s="3">
         <v>44652</v>
       </c>
@@ -11304,7 +11304,7 @@
         <v>1017743</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A414" s="3">
         <v>44682</v>
       </c>
@@ -11327,7 +11327,7 @@
         <v>1963666</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A415" s="3">
         <v>44713</v>
       </c>
@@ -11350,7 +11350,7 @@
         <v>1249758</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A416" s="3">
         <v>44743</v>
       </c>
@@ -11373,7 +11373,7 @@
         <v>2534491</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A417" s="3">
         <v>44774</v>
       </c>
@@ -11396,7 +11396,7 @@
         <v>1193003</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A418" s="3">
         <v>44805</v>
       </c>
@@ -11419,7 +11419,7 @@
         <v>1181484</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A419" s="3">
         <v>44835</v>
       </c>
@@ -11442,7 +11442,7 @@
         <v>1406350</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A420" s="3">
         <v>44866</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>1119802</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A421" s="3">
         <v>44896</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>2499615</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A422" s="3">
         <v>44927</v>
       </c>
@@ -11511,7 +11511,7 @@
         <v>1425949</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A423" s="3">
         <v>44958</v>
       </c>
@@ -11534,7 +11534,7 @@
         <v>1551028</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A424" s="3">
         <v>44986</v>
       </c>
@@ -11557,7 +11557,7 @@
         <v>1056919</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A425" s="3">
         <v>45017</v>
       </c>
@@ -11580,7 +11580,7 @@
         <v>1618756</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A426" s="3">
         <v>45047</v>
       </c>
@@ -11603,7 +11603,7 @@
         <v>988361</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A427" s="3">
         <v>45078</v>
       </c>
@@ -11626,7 +11626,7 @@
         <v>2539286</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A428" s="3">
         <v>45108</v>
       </c>
@@ -11649,7 +11649,7 @@
         <v>1698981</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A429" s="3">
         <v>45139</v>
       </c>
@@ -11672,7 +11672,7 @@
         <v>1575261</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A430" s="3">
         <v>45170</v>
       </c>
@@ -11695,7 +11695,7 @@
         <v>1354115</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A431" s="3">
         <v>45200</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>2838987</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A432" s="3">
         <v>45231</v>
       </c>
@@ -11741,7 +11741,7 @@
         <v>1473908</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A433" s="3">
         <v>45261</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>3665666</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A434" s="3">
         <v>45292</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>2510849</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A435" s="3">
         <v>45323</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>1737690</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A436" s="3">
         <v>45352</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>2104526</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A437" s="3">
         <v>45383</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>1711746</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A438" s="3">
         <v>45413</v>
       </c>
@@ -11879,7 +11879,7 @@
         <v>2141770</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A439" s="3">
         <v>45444</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>1528486</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A440" s="3">
         <v>45474</v>
       </c>
@@ -11925,7 +11925,7 @@
         <v>1078742</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A441" s="3">
         <v>45505</v>
       </c>
@@ -11948,7 +11948,7 @@
         <v>2808595</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A442" s="3">
         <v>45536</v>
       </c>
@@ -11971,7 +11971,7 @@
         <v>2372327</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A443" s="3">
         <v>45566</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>2028511</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A444" s="3">
         <v>45597</v>
       </c>
@@ -12017,7 +12017,7 @@
         <v>2517836</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A445" s="3">
         <v>45627</v>
       </c>
@@ -12040,7 +12040,7 @@
         <v>3093373</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" s="3">
         <v>45658</v>
       </c>
@@ -12063,7 +12063,7 @@
         <v>2478456</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A447" s="3">
         <v>45689</v>
       </c>
@@ -12086,7 +12086,7 @@
         <v>1565522</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A448" s="3">
         <v>45717</v>
       </c>
@@ -12109,7 +12109,7 @@
         <v>3181048</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A449" s="3">
         <v>45748</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>2009245</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A450" s="3">
         <v>45778</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>2239361</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A451" s="3">
         <v>45809</v>
       </c>
@@ -12178,7 +12178,7 @@
         <v>2507081</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A452" s="3">
         <v>45839</v>
       </c>
@@ -12201,7 +12201,7 @@
         <v>2240844</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A453" s="3">
         <v>45870</v>
       </c>
@@ -12224,7 +12224,7 @@
         <v>3125873</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A454" s="3">
         <v>45901</v>
       </c>
@@ -12247,7 +12247,7 @@
         <v>2892852</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A455" s="3">
         <v>45931</v>
       </c>
@@ -12270,7 +12270,7 @@
         <v>4688472</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A456" s="3">
         <v>45962</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>1853757</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A457" s="3">
         <v>45992</v>
       </c>
@@ -12316,7 +12316,7 @@
         <v>3033083</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A458" s="3">
         <v>46023</v>
       </c>
@@ -12339,7 +12339,7 @@
         <v>2476277</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A459" s="3">
         <v>46054</v>
       </c>
@@ -12362,7 +12362,7 @@
         <v>2212546</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A460" s="3">
         <v>46082</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>3525326</v>
       </c>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A461" s="3">
         <v>46113</v>
       </c>
@@ -12408,7 +12408,7 @@
         <v>2897199</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A462" s="3">
         <v>46143</v>
       </c>
@@ -12442,9 +12442,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB7DC0E-2E20-4678-9169-BC7D5B73B843}">
   <dimension ref="A2:F463"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>467</v>
       </c>
@@ -12457,7 +12457,7 @@
       <c r="E2" s="1"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>466</v>
       </c>
@@ -12470,7 +12470,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>465</v>
       </c>
@@ -12483,7 +12483,7 @@
       <c r="E4" s="1"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>464</v>
       </c>
@@ -12496,7 +12496,7 @@
       <c r="E5" s="1"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>463</v>
       </c>
@@ -12509,7 +12509,7 @@
       <c r="E6" s="1"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>462</v>
       </c>
@@ -12522,7 +12522,7 @@
       <c r="E7" s="1"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>461</v>
       </c>
@@ -12535,7 +12535,7 @@
       <c r="E8" s="1"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>460</v>
       </c>
@@ -12548,7 +12548,7 @@
       <c r="E9" s="1"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>459</v>
       </c>
@@ -12561,7 +12561,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>458</v>
       </c>
@@ -12574,7 +12574,7 @@
       <c r="E11" s="1"/>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>457</v>
       </c>
@@ -12587,7 +12587,7 @@
       <c r="E12" s="1"/>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>456</v>
       </c>
@@ -12600,7 +12600,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>455</v>
       </c>
@@ -12613,7 +12613,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>454</v>
       </c>
@@ -12626,7 +12626,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>453</v>
       </c>
@@ -12639,7 +12639,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>452</v>
       </c>
@@ -12652,7 +12652,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>451</v>
       </c>
@@ -12665,7 +12665,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>450</v>
       </c>
@@ -12678,7 +12678,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>449</v>
       </c>
@@ -12691,7 +12691,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>448</v>
       </c>
@@ -12704,7 +12704,7 @@
       <c r="E21" s="1"/>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>447</v>
       </c>
@@ -12717,7 +12717,7 @@
       <c r="E22" s="1"/>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>446</v>
       </c>
@@ -12730,7 +12730,7 @@
       <c r="E23" s="1"/>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>445</v>
       </c>
@@ -12743,7 +12743,7 @@
       <c r="E24" s="1"/>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>444</v>
       </c>
@@ -12756,7 +12756,7 @@
       <c r="E25" s="1"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>443</v>
       </c>
@@ -12769,7 +12769,7 @@
       <c r="E26" s="1"/>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>442</v>
       </c>
@@ -12782,7 +12782,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>441</v>
       </c>
@@ -12795,7 +12795,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>440</v>
       </c>
@@ -12808,7 +12808,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>439</v>
       </c>
@@ -12821,7 +12821,7 @@
       <c r="E30" s="1"/>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>438</v>
       </c>
@@ -12834,7 +12834,7 @@
       <c r="E31" s="1"/>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>437</v>
       </c>
@@ -12847,7 +12847,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>436</v>
       </c>
@@ -12860,7 +12860,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>435</v>
       </c>
@@ -12873,7 +12873,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>434</v>
       </c>
@@ -12886,7 +12886,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>433</v>
       </c>
@@ -12899,7 +12899,7 @@
       <c r="E36" s="1"/>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>432</v>
       </c>
@@ -12912,7 +12912,7 @@
       <c r="E37" s="1"/>
       <c r="F37" s="4"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>431</v>
       </c>
@@ -12925,7 +12925,7 @@
       <c r="E38" s="1"/>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>430</v>
       </c>
@@ -12938,7 +12938,7 @@
       <c r="E39" s="1"/>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>429</v>
       </c>
@@ -12951,7 +12951,7 @@
       <c r="E40" s="1"/>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>428</v>
       </c>
@@ -12964,7 +12964,7 @@
       <c r="E41" s="1"/>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>427</v>
       </c>
@@ -12977,7 +12977,7 @@
       <c r="E42" s="1"/>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>426</v>
       </c>
@@ -12990,7 +12990,7 @@
       <c r="E43" s="1"/>
       <c r="F43" s="4"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>425</v>
       </c>
@@ -13003,7 +13003,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="4"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>424</v>
       </c>
@@ -13016,7 +13016,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="4"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>423</v>
       </c>
@@ -13029,7 +13029,7 @@
       <c r="E46" s="1"/>
       <c r="F46" s="4"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>422</v>
       </c>
@@ -13042,7 +13042,7 @@
       <c r="E47" s="1"/>
       <c r="F47" s="4"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>421</v>
       </c>
@@ -13055,7 +13055,7 @@
       <c r="E48" s="1"/>
       <c r="F48" s="4"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>420</v>
       </c>
@@ -13068,7 +13068,7 @@
       <c r="E49" s="1"/>
       <c r="F49" s="4"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>419</v>
       </c>
@@ -13081,7 +13081,7 @@
       <c r="E50" s="1"/>
       <c r="F50" s="4"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>418</v>
       </c>
@@ -13094,7 +13094,7 @@
       <c r="E51" s="1"/>
       <c r="F51" s="4"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>417</v>
       </c>
@@ -13107,7 +13107,7 @@
       <c r="E52" s="1"/>
       <c r="F52" s="4"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>416</v>
       </c>
@@ -13120,7 +13120,7 @@
       <c r="E53" s="1"/>
       <c r="F53" s="4"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>415</v>
       </c>
@@ -13133,7 +13133,7 @@
       <c r="E54" s="1"/>
       <c r="F54" s="4"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>414</v>
       </c>
@@ -13146,7 +13146,7 @@
       <c r="E55" s="1"/>
       <c r="F55" s="4"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>413</v>
       </c>
@@ -13159,7 +13159,7 @@
       <c r="E56" s="1"/>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>412</v>
       </c>
@@ -13172,7 +13172,7 @@
       <c r="E57" s="1"/>
       <c r="F57" s="4"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>411</v>
       </c>
@@ -13185,7 +13185,7 @@
       <c r="E58" s="1"/>
       <c r="F58" s="4"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>410</v>
       </c>
@@ -13198,7 +13198,7 @@
       <c r="E59" s="1"/>
       <c r="F59" s="4"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>409</v>
       </c>
@@ -13211,7 +13211,7 @@
       <c r="E60" s="1"/>
       <c r="F60" s="4"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>408</v>
       </c>
@@ -13224,7 +13224,7 @@
       <c r="E61" s="1"/>
       <c r="F61" s="4"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>407</v>
       </c>
@@ -13237,7 +13237,7 @@
       <c r="E62" s="1"/>
       <c r="F62" s="4"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>406</v>
       </c>
@@ -13250,7 +13250,7 @@
       <c r="E63" s="1"/>
       <c r="F63" s="4"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>405</v>
       </c>
@@ -13263,7 +13263,7 @@
       <c r="E64" s="1"/>
       <c r="F64" s="4"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>404</v>
       </c>
@@ -13276,7 +13276,7 @@
       <c r="E65" s="1"/>
       <c r="F65" s="4"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>403</v>
       </c>
@@ -13289,7 +13289,7 @@
       <c r="E66" s="1"/>
       <c r="F66" s="4"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>402</v>
       </c>
@@ -13302,7 +13302,7 @@
       <c r="E67" s="1"/>
       <c r="F67" s="4"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>401</v>
       </c>
@@ -13315,7 +13315,7 @@
       <c r="E68" s="1"/>
       <c r="F68" s="4"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>400</v>
       </c>
@@ -13328,7 +13328,7 @@
       <c r="E69" s="1"/>
       <c r="F69" s="4"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>399</v>
       </c>
@@ -13341,7 +13341,7 @@
       <c r="E70" s="1"/>
       <c r="F70" s="4"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>398</v>
       </c>
@@ -13354,7 +13354,7 @@
       <c r="E71" s="1"/>
       <c r="F71" s="4"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>397</v>
       </c>
@@ -13367,7 +13367,7 @@
       <c r="E72" s="1"/>
       <c r="F72" s="4"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>396</v>
       </c>
@@ -13380,7 +13380,7 @@
       <c r="E73" s="1"/>
       <c r="F73" s="4"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>395</v>
       </c>
@@ -13393,7 +13393,7 @@
       <c r="E74" s="1"/>
       <c r="F74" s="4"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>394</v>
       </c>
@@ -13406,7 +13406,7 @@
       <c r="E75" s="1"/>
       <c r="F75" s="4"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>393</v>
       </c>
@@ -13419,7 +13419,7 @@
       <c r="E76" s="1"/>
       <c r="F76" s="4"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>392</v>
       </c>
@@ -13432,7 +13432,7 @@
       <c r="E77" s="1"/>
       <c r="F77" s="4"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>391</v>
       </c>
@@ -13445,7 +13445,7 @@
       <c r="E78" s="1"/>
       <c r="F78" s="4"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>390</v>
       </c>
@@ -13458,7 +13458,7 @@
       <c r="E79" s="1"/>
       <c r="F79" s="4"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>389</v>
       </c>
@@ -13471,7 +13471,7 @@
       <c r="E80" s="1"/>
       <c r="F80" s="4"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>388</v>
       </c>
@@ -13484,7 +13484,7 @@
       <c r="E81" s="1"/>
       <c r="F81" s="4"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>387</v>
       </c>
@@ -13497,7 +13497,7 @@
       <c r="E82" s="1"/>
       <c r="F82" s="4"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>386</v>
       </c>
@@ -13510,7 +13510,7 @@
       <c r="E83" s="1"/>
       <c r="F83" s="4"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>385</v>
       </c>
@@ -13523,7 +13523,7 @@
       <c r="E84" s="1"/>
       <c r="F84" s="4"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>384</v>
       </c>
@@ -13536,7 +13536,7 @@
       <c r="E85" s="1"/>
       <c r="F85" s="4"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>383</v>
       </c>
@@ -13549,7 +13549,7 @@
       <c r="E86" s="1"/>
       <c r="F86" s="4"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>382</v>
       </c>
@@ -13562,7 +13562,7 @@
       <c r="E87" s="1"/>
       <c r="F87" s="4"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>381</v>
       </c>
@@ -13575,7 +13575,7 @@
       <c r="E88" s="1"/>
       <c r="F88" s="4"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>380</v>
       </c>
@@ -13588,7 +13588,7 @@
       <c r="E89" s="1"/>
       <c r="F89" s="4"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>379</v>
       </c>
@@ -13601,7 +13601,7 @@
       <c r="E90" s="1"/>
       <c r="F90" s="4"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>378</v>
       </c>
@@ -13614,7 +13614,7 @@
       <c r="E91" s="1"/>
       <c r="F91" s="4"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>377</v>
       </c>
@@ -13627,7 +13627,7 @@
       <c r="E92" s="1"/>
       <c r="F92" s="4"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>376</v>
       </c>
@@ -13640,7 +13640,7 @@
       <c r="E93" s="1"/>
       <c r="F93" s="4"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>375</v>
       </c>
@@ -13653,7 +13653,7 @@
       <c r="E94" s="1"/>
       <c r="F94" s="4"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>374</v>
       </c>
@@ -13666,7 +13666,7 @@
       <c r="E95" s="1"/>
       <c r="F95" s="4"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>373</v>
       </c>
@@ -13679,7 +13679,7 @@
       <c r="E96" s="1"/>
       <c r="F96" s="4"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>372</v>
       </c>
@@ -13692,7 +13692,7 @@
       <c r="E97" s="1"/>
       <c r="F97" s="4"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>371</v>
       </c>
@@ -13705,7 +13705,7 @@
       <c r="E98" s="1"/>
       <c r="F98" s="4"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>370</v>
       </c>
@@ -13718,7 +13718,7 @@
       <c r="E99" s="1"/>
       <c r="F99" s="4"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>369</v>
       </c>
@@ -13731,7 +13731,7 @@
       <c r="E100" s="1"/>
       <c r="F100" s="4"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>368</v>
       </c>
@@ -13744,7 +13744,7 @@
       <c r="E101" s="1"/>
       <c r="F101" s="4"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>367</v>
       </c>
@@ -13757,7 +13757,7 @@
       <c r="E102" s="1"/>
       <c r="F102" s="4"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>366</v>
       </c>
@@ -13770,7 +13770,7 @@
       <c r="E103" s="1"/>
       <c r="F103" s="4"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>365</v>
       </c>
@@ -13783,7 +13783,7 @@
       <c r="E104" s="1"/>
       <c r="F104" s="4"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>364</v>
       </c>
@@ -13796,7 +13796,7 @@
       <c r="E105" s="1"/>
       <c r="F105" s="4"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>363</v>
       </c>
@@ -13809,7 +13809,7 @@
       <c r="E106" s="1"/>
       <c r="F106" s="4"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>362</v>
       </c>
@@ -13822,7 +13822,7 @@
       <c r="E107" s="1"/>
       <c r="F107" s="4"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>361</v>
       </c>
@@ -13835,7 +13835,7 @@
       <c r="E108" s="1"/>
       <c r="F108" s="4"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>360</v>
       </c>
@@ -13848,7 +13848,7 @@
       <c r="E109" s="1"/>
       <c r="F109" s="4"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>359</v>
       </c>
@@ -13861,7 +13861,7 @@
       <c r="E110" s="1"/>
       <c r="F110" s="4"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>358</v>
       </c>
@@ -13874,7 +13874,7 @@
       <c r="E111" s="1"/>
       <c r="F111" s="4"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>357</v>
       </c>
@@ -13887,7 +13887,7 @@
       <c r="E112" s="1"/>
       <c r="F112" s="4"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>356</v>
       </c>
@@ -13900,7 +13900,7 @@
       <c r="E113" s="1"/>
       <c r="F113" s="4"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>355</v>
       </c>
@@ -13913,7 +13913,7 @@
       <c r="E114" s="1"/>
       <c r="F114" s="4"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>354</v>
       </c>
@@ -13926,7 +13926,7 @@
       <c r="E115" s="1"/>
       <c r="F115" s="4"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>353</v>
       </c>
@@ -13939,7 +13939,7 @@
       <c r="E116" s="1"/>
       <c r="F116" s="4"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>352</v>
       </c>
@@ -13952,7 +13952,7 @@
       <c r="E117" s="1"/>
       <c r="F117" s="4"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>351</v>
       </c>
@@ -13965,7 +13965,7 @@
       <c r="E118" s="1"/>
       <c r="F118" s="4"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>350</v>
       </c>
@@ -13978,7 +13978,7 @@
       <c r="E119" s="1"/>
       <c r="F119" s="4"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>349</v>
       </c>
@@ -13991,7 +13991,7 @@
       <c r="E120" s="1"/>
       <c r="F120" s="4"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>348</v>
       </c>
@@ -14004,7 +14004,7 @@
       <c r="E121" s="1"/>
       <c r="F121" s="4"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>347</v>
       </c>
@@ -14017,7 +14017,7 @@
       <c r="E122" s="1"/>
       <c r="F122" s="4"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>346</v>
       </c>
@@ -14030,7 +14030,7 @@
       <c r="E123" s="1"/>
       <c r="F123" s="4"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>345</v>
       </c>
@@ -14043,7 +14043,7 @@
       <c r="E124" s="1"/>
       <c r="F124" s="4"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>344</v>
       </c>
@@ -14056,7 +14056,7 @@
       <c r="E125" s="1"/>
       <c r="F125" s="4"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>343</v>
       </c>
@@ -14069,7 +14069,7 @@
       <c r="E126" s="1"/>
       <c r="F126" s="4"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>342</v>
       </c>
@@ -14082,7 +14082,7 @@
       <c r="E127" s="1"/>
       <c r="F127" s="4"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>341</v>
       </c>
@@ -14095,7 +14095,7 @@
       <c r="E128" s="1"/>
       <c r="F128" s="4"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>340</v>
       </c>
@@ -14108,7 +14108,7 @@
       <c r="E129" s="1"/>
       <c r="F129" s="4"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>339</v>
       </c>
@@ -14121,7 +14121,7 @@
       <c r="E130" s="1"/>
       <c r="F130" s="4"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>338</v>
       </c>
@@ -14134,7 +14134,7 @@
       <c r="E131" s="1"/>
       <c r="F131" s="4"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>337</v>
       </c>
@@ -14147,7 +14147,7 @@
       <c r="E132" s="1"/>
       <c r="F132" s="4"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>336</v>
       </c>
@@ -14160,7 +14160,7 @@
       <c r="E133" s="1"/>
       <c r="F133" s="4"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>335</v>
       </c>
@@ -14173,7 +14173,7 @@
       <c r="E134" s="1"/>
       <c r="F134" s="4"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>334</v>
       </c>
@@ -14186,7 +14186,7 @@
       <c r="E135" s="1"/>
       <c r="F135" s="4"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>333</v>
       </c>
@@ -14199,7 +14199,7 @@
       <c r="E136" s="1"/>
       <c r="F136" s="4"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>332</v>
       </c>
@@ -14212,7 +14212,7 @@
       <c r="E137" s="1"/>
       <c r="F137" s="4"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>331</v>
       </c>
@@ -14225,7 +14225,7 @@
       <c r="E138" s="1"/>
       <c r="F138" s="4"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>330</v>
       </c>
@@ -14238,7 +14238,7 @@
       <c r="E139" s="1"/>
       <c r="F139" s="4"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>329</v>
       </c>
@@ -14251,7 +14251,7 @@
       <c r="E140" s="1"/>
       <c r="F140" s="4"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>328</v>
       </c>
@@ -14264,7 +14264,7 @@
       <c r="E141" s="1"/>
       <c r="F141" s="4"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>327</v>
       </c>
@@ -14277,7 +14277,7 @@
       <c r="E142" s="1"/>
       <c r="F142" s="4"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>326</v>
       </c>
@@ -14290,7 +14290,7 @@
       <c r="E143" s="1"/>
       <c r="F143" s="4"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>325</v>
       </c>
@@ -14303,7 +14303,7 @@
       <c r="E144" s="1"/>
       <c r="F144" s="4"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>324</v>
       </c>
@@ -14316,7 +14316,7 @@
       <c r="E145" s="1"/>
       <c r="F145" s="4"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>323</v>
       </c>
@@ -14329,7 +14329,7 @@
       <c r="E146" s="1"/>
       <c r="F146" s="4"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>322</v>
       </c>
@@ -14342,7 +14342,7 @@
       <c r="E147" s="1"/>
       <c r="F147" s="4"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>321</v>
       </c>
@@ -14355,7 +14355,7 @@
       <c r="E148" s="1"/>
       <c r="F148" s="4"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>320</v>
       </c>
@@ -14368,7 +14368,7 @@
       <c r="E149" s="1"/>
       <c r="F149" s="4"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>319</v>
       </c>
@@ -14381,7 +14381,7 @@
       <c r="E150" s="1"/>
       <c r="F150" s="4"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>318</v>
       </c>
@@ -14394,7 +14394,7 @@
       <c r="E151" s="1"/>
       <c r="F151" s="4"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>317</v>
       </c>
@@ -14407,7 +14407,7 @@
       <c r="E152" s="1"/>
       <c r="F152" s="4"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>316</v>
       </c>
@@ -14420,7 +14420,7 @@
       <c r="E153" s="1"/>
       <c r="F153" s="4"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>315</v>
       </c>
@@ -14433,7 +14433,7 @@
       <c r="E154" s="1"/>
       <c r="F154" s="4"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>314</v>
       </c>
@@ -14446,7 +14446,7 @@
       <c r="E155" s="1"/>
       <c r="F155" s="4"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>313</v>
       </c>
@@ -14459,7 +14459,7 @@
       <c r="E156" s="1"/>
       <c r="F156" s="4"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>312</v>
       </c>
@@ -14472,7 +14472,7 @@
       <c r="E157" s="1"/>
       <c r="F157" s="4"/>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>311</v>
       </c>
@@ -14485,7 +14485,7 @@
       <c r="E158" s="1"/>
       <c r="F158" s="4"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>310</v>
       </c>
@@ -14498,7 +14498,7 @@
       <c r="E159" s="1"/>
       <c r="F159" s="4"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>309</v>
       </c>
@@ -14511,7 +14511,7 @@
       <c r="E160" s="1"/>
       <c r="F160" s="4"/>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>308</v>
       </c>
@@ -14524,7 +14524,7 @@
       <c r="E161" s="1"/>
       <c r="F161" s="4"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>307</v>
       </c>
@@ -14537,7 +14537,7 @@
       <c r="E162" s="1"/>
       <c r="F162" s="4"/>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>306</v>
       </c>
@@ -14550,7 +14550,7 @@
       <c r="E163" s="1"/>
       <c r="F163" s="4"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>305</v>
       </c>
@@ -14563,7 +14563,7 @@
       <c r="E164" s="1"/>
       <c r="F164" s="4"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>304</v>
       </c>
@@ -14576,7 +14576,7 @@
       <c r="E165" s="1"/>
       <c r="F165" s="4"/>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>303</v>
       </c>
@@ -14589,7 +14589,7 @@
       <c r="E166" s="1"/>
       <c r="F166" s="4"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>302</v>
       </c>
@@ -14602,7 +14602,7 @@
       <c r="E167" s="1"/>
       <c r="F167" s="4"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>301</v>
       </c>
@@ -14615,7 +14615,7 @@
       <c r="E168" s="1"/>
       <c r="F168" s="4"/>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>300</v>
       </c>
@@ -14628,7 +14628,7 @@
       <c r="E169" s="1"/>
       <c r="F169" s="4"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>299</v>
       </c>
@@ -14641,7 +14641,7 @@
       <c r="E170" s="1"/>
       <c r="F170" s="4"/>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>298</v>
       </c>
@@ -14654,7 +14654,7 @@
       <c r="E171" s="1"/>
       <c r="F171" s="4"/>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>297</v>
       </c>
@@ -14667,7 +14667,7 @@
       <c r="E172" s="1"/>
       <c r="F172" s="4"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>296</v>
       </c>
@@ -14680,7 +14680,7 @@
       <c r="E173" s="1"/>
       <c r="F173" s="4"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>295</v>
       </c>
@@ -14693,7 +14693,7 @@
       <c r="E174" s="1"/>
       <c r="F174" s="4"/>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>294</v>
       </c>
@@ -14706,7 +14706,7 @@
       <c r="E175" s="1"/>
       <c r="F175" s="4"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>293</v>
       </c>
@@ -14719,7 +14719,7 @@
       <c r="E176" s="1"/>
       <c r="F176" s="4"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>292</v>
       </c>
@@ -14732,7 +14732,7 @@
       <c r="E177" s="1"/>
       <c r="F177" s="4"/>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>291</v>
       </c>
@@ -14745,7 +14745,7 @@
       <c r="E178" s="1"/>
       <c r="F178" s="4"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>290</v>
       </c>
@@ -14758,7 +14758,7 @@
       <c r="E179" s="1"/>
       <c r="F179" s="4"/>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>289</v>
       </c>
@@ -14771,7 +14771,7 @@
       <c r="E180" s="1"/>
       <c r="F180" s="4"/>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>288</v>
       </c>
@@ -14784,7 +14784,7 @@
       <c r="E181" s="1"/>
       <c r="F181" s="4"/>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>287</v>
       </c>
@@ -14797,7 +14797,7 @@
       <c r="E182" s="1"/>
       <c r="F182" s="4"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>286</v>
       </c>
@@ -14810,7 +14810,7 @@
       <c r="E183" s="1"/>
       <c r="F183" s="4"/>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>285</v>
       </c>
@@ -14823,7 +14823,7 @@
       <c r="E184" s="1"/>
       <c r="F184" s="4"/>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>284</v>
       </c>
@@ -14836,7 +14836,7 @@
       <c r="E185" s="1"/>
       <c r="F185" s="4"/>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>283</v>
       </c>
@@ -14849,7 +14849,7 @@
       <c r="E186" s="1"/>
       <c r="F186" s="4"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>282</v>
       </c>
@@ -14862,7 +14862,7 @@
       <c r="E187" s="1"/>
       <c r="F187" s="4"/>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>281</v>
       </c>
@@ -14875,7 +14875,7 @@
       <c r="E188" s="1"/>
       <c r="F188" s="4"/>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>280</v>
       </c>
@@ -14888,7 +14888,7 @@
       <c r="E189" s="1"/>
       <c r="F189" s="4"/>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>279</v>
       </c>
@@ -14901,7 +14901,7 @@
       <c r="E190" s="1"/>
       <c r="F190" s="4"/>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>278</v>
       </c>
@@ -14914,7 +14914,7 @@
       <c r="E191" s="1"/>
       <c r="F191" s="4"/>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>277</v>
       </c>
@@ -14927,7 +14927,7 @@
       <c r="E192" s="1"/>
       <c r="F192" s="4"/>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>276</v>
       </c>
@@ -14940,7 +14940,7 @@
       <c r="E193" s="1"/>
       <c r="F193" s="4"/>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>275</v>
       </c>
@@ -14953,7 +14953,7 @@
       <c r="E194" s="1"/>
       <c r="F194" s="4"/>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>274</v>
       </c>
@@ -14966,7 +14966,7 @@
       <c r="E195" s="1"/>
       <c r="F195" s="4"/>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>273</v>
       </c>
@@ -14979,7 +14979,7 @@
       <c r="E196" s="1"/>
       <c r="F196" s="4"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>272</v>
       </c>
@@ -14992,7 +14992,7 @@
       <c r="E197" s="1"/>
       <c r="F197" s="4"/>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>271</v>
       </c>
@@ -15005,7 +15005,7 @@
       <c r="E198" s="1"/>
       <c r="F198" s="4"/>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>270</v>
       </c>
@@ -15018,7 +15018,7 @@
       <c r="E199" s="1"/>
       <c r="F199" s="4"/>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>269</v>
       </c>
@@ -15031,7 +15031,7 @@
       <c r="E200" s="1"/>
       <c r="F200" s="4"/>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>268</v>
       </c>
@@ -15044,7 +15044,7 @@
       <c r="E201" s="1"/>
       <c r="F201" s="4"/>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>267</v>
       </c>
@@ -15057,7 +15057,7 @@
       <c r="E202" s="1"/>
       <c r="F202" s="4"/>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>266</v>
       </c>
@@ -15070,7 +15070,7 @@
       <c r="E203" s="1"/>
       <c r="F203" s="4"/>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>265</v>
       </c>
@@ -15083,7 +15083,7 @@
       <c r="E204" s="1"/>
       <c r="F204" s="4"/>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>264</v>
       </c>
@@ -15096,7 +15096,7 @@
       <c r="E205" s="1"/>
       <c r="F205" s="4"/>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>263</v>
       </c>
@@ -15109,7 +15109,7 @@
       <c r="E206" s="1"/>
       <c r="F206" s="4"/>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>262</v>
       </c>
@@ -15122,7 +15122,7 @@
       <c r="E207" s="1"/>
       <c r="F207" s="4"/>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>261</v>
       </c>
@@ -15135,7 +15135,7 @@
       <c r="E208" s="1"/>
       <c r="F208" s="4"/>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>260</v>
       </c>
@@ -15148,7 +15148,7 @@
       <c r="E209" s="1"/>
       <c r="F209" s="4"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>259</v>
       </c>
@@ -15161,7 +15161,7 @@
       <c r="E210" s="1"/>
       <c r="F210" s="4"/>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>258</v>
       </c>
@@ -15174,7 +15174,7 @@
       <c r="E211" s="1"/>
       <c r="F211" s="4"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>257</v>
       </c>
@@ -15187,7 +15187,7 @@
       <c r="E212" s="1"/>
       <c r="F212" s="4"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>256</v>
       </c>
@@ -15200,7 +15200,7 @@
       <c r="E213" s="1"/>
       <c r="F213" s="4"/>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>255</v>
       </c>
@@ -15213,7 +15213,7 @@
       <c r="E214" s="1"/>
       <c r="F214" s="4"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>254</v>
       </c>
@@ -15226,7 +15226,7 @@
       <c r="E215" s="1"/>
       <c r="F215" s="4"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>253</v>
       </c>
@@ -15239,7 +15239,7 @@
       <c r="E216" s="1"/>
       <c r="F216" s="4"/>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>252</v>
       </c>
@@ -15252,7 +15252,7 @@
       <c r="E217" s="1"/>
       <c r="F217" s="4"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>251</v>
       </c>
@@ -15265,7 +15265,7 @@
       <c r="E218" s="1"/>
       <c r="F218" s="4"/>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>250</v>
       </c>
@@ -15278,7 +15278,7 @@
       <c r="E219" s="1"/>
       <c r="F219" s="4"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>249</v>
       </c>
@@ -15291,7 +15291,7 @@
       <c r="E220" s="1"/>
       <c r="F220" s="4"/>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>248</v>
       </c>
@@ -15304,7 +15304,7 @@
       <c r="E221" s="1"/>
       <c r="F221" s="4"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>247</v>
       </c>
@@ -15317,7 +15317,7 @@
       <c r="E222" s="1"/>
       <c r="F222" s="4"/>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>246</v>
       </c>
@@ -15330,7 +15330,7 @@
       <c r="E223" s="1"/>
       <c r="F223" s="4"/>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>245</v>
       </c>
@@ -15343,7 +15343,7 @@
       <c r="E224" s="1"/>
       <c r="F224" s="4"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>244</v>
       </c>
@@ -15356,7 +15356,7 @@
       <c r="E225" s="1"/>
       <c r="F225" s="4"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>243</v>
       </c>
@@ -15369,7 +15369,7 @@
       <c r="E226" s="1"/>
       <c r="F226" s="4"/>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>242</v>
       </c>
@@ -15382,7 +15382,7 @@
       <c r="E227" s="1"/>
       <c r="F227" s="4"/>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>241</v>
       </c>
@@ -15395,7 +15395,7 @@
       <c r="E228" s="1"/>
       <c r="F228" s="4"/>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>240</v>
       </c>
@@ -15408,7 +15408,7 @@
       <c r="E229" s="1"/>
       <c r="F229" s="4"/>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>239</v>
       </c>
@@ -15421,7 +15421,7 @@
       <c r="E230" s="1"/>
       <c r="F230" s="4"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>238</v>
       </c>
@@ -15434,7 +15434,7 @@
       <c r="E231" s="1"/>
       <c r="F231" s="4"/>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>237</v>
       </c>
@@ -15447,7 +15447,7 @@
       <c r="E232" s="1"/>
       <c r="F232" s="4"/>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>236</v>
       </c>
@@ -15460,7 +15460,7 @@
       <c r="E233" s="1"/>
       <c r="F233" s="4"/>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>235</v>
       </c>
@@ -15473,7 +15473,7 @@
       <c r="E234" s="1"/>
       <c r="F234" s="4"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>234</v>
       </c>
@@ -15486,7 +15486,7 @@
       <c r="E235" s="1"/>
       <c r="F235" s="4"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>233</v>
       </c>
@@ -15499,7 +15499,7 @@
       <c r="E236" s="1"/>
       <c r="F236" s="4"/>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>232</v>
       </c>
@@ -15512,7 +15512,7 @@
       <c r="E237" s="1"/>
       <c r="F237" s="4"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>231</v>
       </c>
@@ -15525,7 +15525,7 @@
       <c r="E238" s="1"/>
       <c r="F238" s="4"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>230</v>
       </c>
@@ -15538,7 +15538,7 @@
       <c r="E239" s="1"/>
       <c r="F239" s="4"/>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>229</v>
       </c>
@@ -15551,7 +15551,7 @@
       <c r="E240" s="1"/>
       <c r="F240" s="4"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>228</v>
       </c>
@@ -15564,7 +15564,7 @@
       <c r="E241" s="1"/>
       <c r="F241" s="4"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>227</v>
       </c>
@@ -15577,7 +15577,7 @@
       <c r="E242" s="1"/>
       <c r="F242" s="4"/>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>226</v>
       </c>
@@ -15590,7 +15590,7 @@
       <c r="E243" s="1"/>
       <c r="F243" s="4"/>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>225</v>
       </c>
@@ -15603,7 +15603,7 @@
       <c r="E244" s="1"/>
       <c r="F244" s="4"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>224</v>
       </c>
@@ -15616,7 +15616,7 @@
       <c r="E245" s="1"/>
       <c r="F245" s="4"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>223</v>
       </c>
@@ -15629,7 +15629,7 @@
       <c r="E246" s="1"/>
       <c r="F246" s="4"/>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>222</v>
       </c>
@@ -15642,7 +15642,7 @@
       <c r="E247" s="1"/>
       <c r="F247" s="4"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>221</v>
       </c>
@@ -15655,7 +15655,7 @@
       <c r="E248" s="1"/>
       <c r="F248" s="4"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>220</v>
       </c>
@@ -15668,7 +15668,7 @@
       <c r="E249" s="1"/>
       <c r="F249" s="4"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>219</v>
       </c>
@@ -15681,7 +15681,7 @@
       <c r="E250" s="1"/>
       <c r="F250" s="4"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>218</v>
       </c>
@@ -15694,7 +15694,7 @@
       <c r="E251" s="1"/>
       <c r="F251" s="4"/>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>217</v>
       </c>
@@ -15707,7 +15707,7 @@
       <c r="E252" s="1"/>
       <c r="F252" s="4"/>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>216</v>
       </c>
@@ -15720,7 +15720,7 @@
       <c r="E253" s="1"/>
       <c r="F253" s="4"/>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>215</v>
       </c>
@@ -15733,7 +15733,7 @@
       <c r="E254" s="1"/>
       <c r="F254" s="4"/>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>214</v>
       </c>
@@ -15746,7 +15746,7 @@
       <c r="E255" s="1"/>
       <c r="F255" s="4"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>213</v>
       </c>
@@ -15759,7 +15759,7 @@
       <c r="E256" s="1"/>
       <c r="F256" s="4"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>212</v>
       </c>
@@ -15772,7 +15772,7 @@
       <c r="E257" s="1"/>
       <c r="F257" s="4"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>211</v>
       </c>
@@ -15785,7 +15785,7 @@
       <c r="E258" s="1"/>
       <c r="F258" s="4"/>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>210</v>
       </c>
@@ -15798,7 +15798,7 @@
       <c r="E259" s="1"/>
       <c r="F259" s="4"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>209</v>
       </c>
@@ -15811,7 +15811,7 @@
       <c r="E260" s="1"/>
       <c r="F260" s="4"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>208</v>
       </c>
@@ -15824,7 +15824,7 @@
       <c r="E261" s="1"/>
       <c r="F261" s="4"/>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>207</v>
       </c>
@@ -15837,7 +15837,7 @@
       <c r="E262" s="1"/>
       <c r="F262" s="4"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>206</v>
       </c>
@@ -15850,7 +15850,7 @@
       <c r="E263" s="1"/>
       <c r="F263" s="4"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>205</v>
       </c>
@@ -15863,7 +15863,7 @@
       <c r="E264" s="1"/>
       <c r="F264" s="4"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>204</v>
       </c>
@@ -15876,7 +15876,7 @@
       <c r="E265" s="1"/>
       <c r="F265" s="4"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>203</v>
       </c>
@@ -15889,7 +15889,7 @@
       <c r="E266" s="1"/>
       <c r="F266" s="4"/>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>202</v>
       </c>
@@ -15902,7 +15902,7 @@
       <c r="E267" s="1"/>
       <c r="F267" s="4"/>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>201</v>
       </c>
@@ -15915,7 +15915,7 @@
       <c r="E268" s="1"/>
       <c r="F268" s="4"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>200</v>
       </c>
@@ -15928,7 +15928,7 @@
       <c r="E269" s="1"/>
       <c r="F269" s="4"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>199</v>
       </c>
@@ -15941,7 +15941,7 @@
       <c r="E270" s="1"/>
       <c r="F270" s="4"/>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>198</v>
       </c>
@@ -15954,7 +15954,7 @@
       <c r="E271" s="1"/>
       <c r="F271" s="4"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>197</v>
       </c>
@@ -15967,7 +15967,7 @@
       <c r="E272" s="1"/>
       <c r="F272" s="4"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>196</v>
       </c>
@@ -15980,7 +15980,7 @@
       <c r="E273" s="1"/>
       <c r="F273" s="4"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>195</v>
       </c>
@@ -15993,7 +15993,7 @@
       <c r="E274" s="1"/>
       <c r="F274" s="4"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>194</v>
       </c>
@@ -16006,7 +16006,7 @@
       <c r="E275" s="1"/>
       <c r="F275" s="4"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>193</v>
       </c>
@@ -16019,7 +16019,7 @@
       <c r="E276" s="1"/>
       <c r="F276" s="4"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>192</v>
       </c>
@@ -16032,7 +16032,7 @@
       <c r="E277" s="1"/>
       <c r="F277" s="4"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>191</v>
       </c>
@@ -16045,7 +16045,7 @@
       <c r="E278" s="1"/>
       <c r="F278" s="4"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>190</v>
       </c>
@@ -16058,7 +16058,7 @@
       <c r="E279" s="1"/>
       <c r="F279" s="4"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>189</v>
       </c>
@@ -16071,7 +16071,7 @@
       <c r="E280" s="1"/>
       <c r="F280" s="4"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>188</v>
       </c>
@@ -16084,7 +16084,7 @@
       <c r="E281" s="1"/>
       <c r="F281" s="4"/>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>187</v>
       </c>
@@ -16097,7 +16097,7 @@
       <c r="E282" s="1"/>
       <c r="F282" s="4"/>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>186</v>
       </c>
@@ -16110,7 +16110,7 @@
       <c r="E283" s="1"/>
       <c r="F283" s="4"/>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>185</v>
       </c>
@@ -16123,7 +16123,7 @@
       <c r="E284" s="1"/>
       <c r="F284" s="4"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>184</v>
       </c>
@@ -16136,7 +16136,7 @@
       <c r="E285" s="1"/>
       <c r="F285" s="4"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>183</v>
       </c>
@@ -16149,7 +16149,7 @@
       <c r="E286" s="1"/>
       <c r="F286" s="4"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>182</v>
       </c>
@@ -16162,7 +16162,7 @@
       <c r="E287" s="1"/>
       <c r="F287" s="4"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>181</v>
       </c>
@@ -16175,7 +16175,7 @@
       <c r="E288" s="1"/>
       <c r="F288" s="4"/>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>180</v>
       </c>
@@ -16188,7 +16188,7 @@
       <c r="E289" s="1"/>
       <c r="F289" s="4"/>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>179</v>
       </c>
@@ -16201,7 +16201,7 @@
       <c r="E290" s="1"/>
       <c r="F290" s="4"/>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>178</v>
       </c>
@@ -16214,7 +16214,7 @@
       <c r="E291" s="1"/>
       <c r="F291" s="4"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>177</v>
       </c>
@@ -16227,7 +16227,7 @@
       <c r="E292" s="1"/>
       <c r="F292" s="4"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>176</v>
       </c>
@@ -16240,7 +16240,7 @@
       <c r="E293" s="1"/>
       <c r="F293" s="4"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>175</v>
       </c>
@@ -16253,7 +16253,7 @@
       <c r="E294" s="1"/>
       <c r="F294" s="4"/>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>174</v>
       </c>
@@ -16266,7 +16266,7 @@
       <c r="E295" s="1"/>
       <c r="F295" s="4"/>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>173</v>
       </c>
@@ -16279,7 +16279,7 @@
       <c r="E296" s="1"/>
       <c r="F296" s="4"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>172</v>
       </c>
@@ -16292,7 +16292,7 @@
       <c r="E297" s="1"/>
       <c r="F297" s="4"/>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>171</v>
       </c>
@@ -16305,7 +16305,7 @@
       <c r="E298" s="1"/>
       <c r="F298" s="4"/>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>170</v>
       </c>
@@ -16318,7 +16318,7 @@
       <c r="E299" s="1"/>
       <c r="F299" s="4"/>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>169</v>
       </c>
@@ -16331,7 +16331,7 @@
       <c r="E300" s="1"/>
       <c r="F300" s="4"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>168</v>
       </c>
@@ -16344,7 +16344,7 @@
       <c r="E301" s="1"/>
       <c r="F301" s="4"/>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>167</v>
       </c>
@@ -16357,7 +16357,7 @@
       <c r="E302" s="1"/>
       <c r="F302" s="4"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>166</v>
       </c>
@@ -16370,7 +16370,7 @@
       <c r="E303" s="1"/>
       <c r="F303" s="4"/>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>165</v>
       </c>
@@ -16383,7 +16383,7 @@
       <c r="E304" s="1"/>
       <c r="F304" s="4"/>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>164</v>
       </c>
@@ -16396,7 +16396,7 @@
       <c r="E305" s="1"/>
       <c r="F305" s="4"/>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>163</v>
       </c>
@@ -16409,7 +16409,7 @@
       <c r="E306" s="1"/>
       <c r="F306" s="4"/>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>162</v>
       </c>
@@ -16422,7 +16422,7 @@
       <c r="E307" s="1"/>
       <c r="F307" s="4"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>161</v>
       </c>
@@ -16435,7 +16435,7 @@
       <c r="E308" s="1"/>
       <c r="F308" s="4"/>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>160</v>
       </c>
@@ -16448,7 +16448,7 @@
       <c r="E309" s="1"/>
       <c r="F309" s="4"/>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>159</v>
       </c>
@@ -16461,7 +16461,7 @@
       <c r="E310" s="1"/>
       <c r="F310" s="4"/>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>158</v>
       </c>
@@ -16474,7 +16474,7 @@
       <c r="E311" s="1"/>
       <c r="F311" s="4"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>157</v>
       </c>
@@ -16487,7 +16487,7 @@
       <c r="E312" s="1"/>
       <c r="F312" s="4"/>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>156</v>
       </c>
@@ -16500,7 +16500,7 @@
       <c r="E313" s="1"/>
       <c r="F313" s="4"/>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>155</v>
       </c>
@@ -16513,7 +16513,7 @@
       <c r="E314" s="1"/>
       <c r="F314" s="4"/>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>154</v>
       </c>
@@ -16526,7 +16526,7 @@
       <c r="E315" s="1"/>
       <c r="F315" s="4"/>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>153</v>
       </c>
@@ -16539,7 +16539,7 @@
       <c r="E316" s="1"/>
       <c r="F316" s="4"/>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>152</v>
       </c>
@@ -16552,7 +16552,7 @@
       <c r="E317" s="1"/>
       <c r="F317" s="4"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>151</v>
       </c>
@@ -16565,7 +16565,7 @@
       <c r="E318" s="1"/>
       <c r="F318" s="4"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>150</v>
       </c>
@@ -16578,7 +16578,7 @@
       <c r="E319" s="1"/>
       <c r="F319" s="4"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>149</v>
       </c>
@@ -16591,7 +16591,7 @@
       <c r="E320" s="1"/>
       <c r="F320" s="4"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>148</v>
       </c>
@@ -16604,7 +16604,7 @@
       <c r="E321" s="1"/>
       <c r="F321" s="4"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>147</v>
       </c>
@@ -16617,7 +16617,7 @@
       <c r="E322" s="1"/>
       <c r="F322" s="4"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>146</v>
       </c>
@@ -16630,7 +16630,7 @@
       <c r="E323" s="1"/>
       <c r="F323" s="4"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>145</v>
       </c>
@@ -16643,7 +16643,7 @@
       <c r="E324" s="1"/>
       <c r="F324" s="4"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>144</v>
       </c>
@@ -16656,7 +16656,7 @@
       <c r="E325" s="1"/>
       <c r="F325" s="4"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>143</v>
       </c>
@@ -16669,7 +16669,7 @@
       <c r="E326" s="1"/>
       <c r="F326" s="4"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>142</v>
       </c>
@@ -16682,7 +16682,7 @@
       <c r="E327" s="1"/>
       <c r="F327" s="4"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>141</v>
       </c>
@@ -16695,7 +16695,7 @@
       <c r="E328" s="1"/>
       <c r="F328" s="4"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>140</v>
       </c>
@@ -16708,7 +16708,7 @@
       <c r="E329" s="1"/>
       <c r="F329" s="4"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>139</v>
       </c>
@@ -16721,7 +16721,7 @@
       <c r="E330" s="1"/>
       <c r="F330" s="4"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>138</v>
       </c>
@@ -16734,7 +16734,7 @@
       <c r="E331" s="1"/>
       <c r="F331" s="4"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>137</v>
       </c>
@@ -16747,7 +16747,7 @@
       <c r="E332" s="1"/>
       <c r="F332" s="4"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>136</v>
       </c>
@@ -16760,7 +16760,7 @@
       <c r="E333" s="1"/>
       <c r="F333" s="4"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>135</v>
       </c>
@@ -16773,7 +16773,7 @@
       <c r="E334" s="1"/>
       <c r="F334" s="4"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>134</v>
       </c>
@@ -16786,7 +16786,7 @@
       <c r="E335" s="1"/>
       <c r="F335" s="4"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>133</v>
       </c>
@@ -16799,7 +16799,7 @@
       <c r="E336" s="1"/>
       <c r="F336" s="4"/>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>132</v>
       </c>
@@ -16812,7 +16812,7 @@
       <c r="E337" s="1"/>
       <c r="F337" s="4"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>131</v>
       </c>
@@ -16825,7 +16825,7 @@
       <c r="E338" s="1"/>
       <c r="F338" s="4"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>130</v>
       </c>
@@ -16838,7 +16838,7 @@
       <c r="E339" s="1"/>
       <c r="F339" s="4"/>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>129</v>
       </c>
@@ -16851,7 +16851,7 @@
       <c r="E340" s="1"/>
       <c r="F340" s="4"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>128</v>
       </c>
@@ -16864,7 +16864,7 @@
       <c r="E341" s="1"/>
       <c r="F341" s="4"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>127</v>
       </c>
@@ -16877,7 +16877,7 @@
       <c r="E342" s="1"/>
       <c r="F342" s="4"/>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>126</v>
       </c>
@@ -16890,7 +16890,7 @@
       <c r="E343" s="1"/>
       <c r="F343" s="4"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>125</v>
       </c>
@@ -16903,7 +16903,7 @@
       <c r="E344" s="1"/>
       <c r="F344" s="4"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>124</v>
       </c>
@@ -16916,7 +16916,7 @@
       <c r="E345" s="1"/>
       <c r="F345" s="4"/>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>123</v>
       </c>
@@ -16929,7 +16929,7 @@
       <c r="E346" s="1"/>
       <c r="F346" s="4"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>122</v>
       </c>
@@ -16942,7 +16942,7 @@
       <c r="E347" s="1"/>
       <c r="F347" s="4"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>121</v>
       </c>
@@ -16955,7 +16955,7 @@
       <c r="E348" s="1"/>
       <c r="F348" s="4"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>120</v>
       </c>
@@ -16968,7 +16968,7 @@
       <c r="E349" s="1"/>
       <c r="F349" s="4"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>119</v>
       </c>
@@ -16981,7 +16981,7 @@
       <c r="E350" s="1"/>
       <c r="F350" s="4"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>118</v>
       </c>
@@ -16994,7 +16994,7 @@
       <c r="E351" s="1"/>
       <c r="F351" s="4"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>117</v>
       </c>
@@ -17007,7 +17007,7 @@
       <c r="E352" s="1"/>
       <c r="F352" s="4"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>116</v>
       </c>
@@ -17020,7 +17020,7 @@
       <c r="E353" s="1"/>
       <c r="F353" s="4"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>115</v>
       </c>
@@ -17033,7 +17033,7 @@
       <c r="E354" s="1"/>
       <c r="F354" s="4"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>114</v>
       </c>
@@ -17046,7 +17046,7 @@
       <c r="E355" s="1"/>
       <c r="F355" s="4"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>113</v>
       </c>
@@ -17059,7 +17059,7 @@
       <c r="E356" s="1"/>
       <c r="F356" s="4"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>112</v>
       </c>
@@ -17072,7 +17072,7 @@
       <c r="E357" s="1"/>
       <c r="F357" s="4"/>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>111</v>
       </c>
@@ -17085,7 +17085,7 @@
       <c r="E358" s="1"/>
       <c r="F358" s="4"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>110</v>
       </c>
@@ -17098,7 +17098,7 @@
       <c r="E359" s="1"/>
       <c r="F359" s="4"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>109</v>
       </c>
@@ -17111,7 +17111,7 @@
       <c r="E360" s="1"/>
       <c r="F360" s="4"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>108</v>
       </c>
@@ -17124,7 +17124,7 @@
       <c r="E361" s="1"/>
       <c r="F361" s="4"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>107</v>
       </c>
@@ -17137,7 +17137,7 @@
       <c r="E362" s="1"/>
       <c r="F362" s="4"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>106</v>
       </c>
@@ -17150,7 +17150,7 @@
       <c r="E363" s="1"/>
       <c r="F363" s="4"/>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>105</v>
       </c>
@@ -17163,7 +17163,7 @@
       <c r="E364" s="1"/>
       <c r="F364" s="4"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>104</v>
       </c>
@@ -17176,7 +17176,7 @@
       <c r="E365" s="1"/>
       <c r="F365" s="4"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>103</v>
       </c>
@@ -17189,7 +17189,7 @@
       <c r="E366" s="1"/>
       <c r="F366" s="4"/>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>102</v>
       </c>
@@ -17202,7 +17202,7 @@
       <c r="E367" s="1"/>
       <c r="F367" s="4"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>101</v>
       </c>
@@ -17215,7 +17215,7 @@
       <c r="E368" s="1"/>
       <c r="F368" s="4"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>100</v>
       </c>
@@ -17228,7 +17228,7 @@
       <c r="E369" s="1"/>
       <c r="F369" s="4"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>99</v>
       </c>
@@ -17241,7 +17241,7 @@
       <c r="E370" s="1"/>
       <c r="F370" s="4"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>98</v>
       </c>
@@ -17254,7 +17254,7 @@
       <c r="E371" s="1"/>
       <c r="F371" s="4"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>97</v>
       </c>
@@ -17267,7 +17267,7 @@
       <c r="E372" s="1"/>
       <c r="F372" s="4"/>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>96</v>
       </c>
@@ -17280,7 +17280,7 @@
       <c r="E373" s="1"/>
       <c r="F373" s="4"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>95</v>
       </c>
@@ -17293,7 +17293,7 @@
       <c r="E374" s="1"/>
       <c r="F374" s="4"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>94</v>
       </c>
@@ -17306,7 +17306,7 @@
       <c r="E375" s="1"/>
       <c r="F375" s="4"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>93</v>
       </c>
@@ -17319,7 +17319,7 @@
       <c r="E376" s="1"/>
       <c r="F376" s="4"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>92</v>
       </c>
@@ -17332,7 +17332,7 @@
       <c r="E377" s="1"/>
       <c r="F377" s="4"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>91</v>
       </c>
@@ -17345,7 +17345,7 @@
       <c r="E378" s="1"/>
       <c r="F378" s="4"/>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>90</v>
       </c>
@@ -17358,7 +17358,7 @@
       <c r="E379" s="1"/>
       <c r="F379" s="4"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>89</v>
       </c>
@@ -17371,7 +17371,7 @@
       <c r="E380" s="1"/>
       <c r="F380" s="4"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>88</v>
       </c>
@@ -17384,7 +17384,7 @@
       <c r="E381" s="1"/>
       <c r="F381" s="4"/>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>87</v>
       </c>
@@ -17397,7 +17397,7 @@
       <c r="E382" s="1"/>
       <c r="F382" s="4"/>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>86</v>
       </c>
@@ -17410,7 +17410,7 @@
       <c r="E383" s="1"/>
       <c r="F383" s="4"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>85</v>
       </c>
@@ -17423,7 +17423,7 @@
       <c r="E384" s="1"/>
       <c r="F384" s="4"/>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>84</v>
       </c>
@@ -17436,7 +17436,7 @@
       <c r="E385" s="1"/>
       <c r="F385" s="4"/>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>83</v>
       </c>
@@ -17449,7 +17449,7 @@
       <c r="E386" s="1"/>
       <c r="F386" s="4"/>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>82</v>
       </c>
@@ -17462,7 +17462,7 @@
       <c r="E387" s="1"/>
       <c r="F387" s="4"/>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>81</v>
       </c>
@@ -17475,7 +17475,7 @@
       <c r="E388" s="1"/>
       <c r="F388" s="4"/>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>80</v>
       </c>
@@ -17488,7 +17488,7 @@
       <c r="E389" s="1"/>
       <c r="F389" s="4"/>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>79</v>
       </c>
@@ -17501,7 +17501,7 @@
       <c r="E390" s="1"/>
       <c r="F390" s="4"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>78</v>
       </c>
@@ -17514,7 +17514,7 @@
       <c r="E391" s="1"/>
       <c r="F391" s="4"/>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>77</v>
       </c>
@@ -17527,7 +17527,7 @@
       <c r="E392" s="1"/>
       <c r="F392" s="4"/>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>76</v>
       </c>
@@ -17540,7 +17540,7 @@
       <c r="E393" s="1"/>
       <c r="F393" s="4"/>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>75</v>
       </c>
@@ -17553,7 +17553,7 @@
       <c r="E394" s="1"/>
       <c r="F394" s="4"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>74</v>
       </c>
@@ -17566,7 +17566,7 @@
       <c r="E395" s="1"/>
       <c r="F395" s="4"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>73</v>
       </c>
@@ -17579,7 +17579,7 @@
       <c r="E396" s="1"/>
       <c r="F396" s="4"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>72</v>
       </c>
@@ -17592,7 +17592,7 @@
       <c r="E397" s="1"/>
       <c r="F397" s="4"/>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>71</v>
       </c>
@@ -17605,7 +17605,7 @@
       <c r="E398" s="1"/>
       <c r="F398" s="4"/>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>70</v>
       </c>
@@ -17618,7 +17618,7 @@
       <c r="E399" s="1"/>
       <c r="F399" s="4"/>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>69</v>
       </c>
@@ -17631,7 +17631,7 @@
       <c r="E400" s="1"/>
       <c r="F400" s="4"/>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>68</v>
       </c>
@@ -17644,7 +17644,7 @@
       <c r="E401" s="1"/>
       <c r="F401" s="4"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>67</v>
       </c>
@@ -17657,7 +17657,7 @@
       <c r="E402" s="1"/>
       <c r="F402" s="4"/>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>66</v>
       </c>
@@ -17670,7 +17670,7 @@
       <c r="E403" s="1"/>
       <c r="F403" s="4"/>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>65</v>
       </c>
@@ -17683,7 +17683,7 @@
       <c r="E404" s="1"/>
       <c r="F404" s="4"/>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>64</v>
       </c>
@@ -17696,7 +17696,7 @@
       <c r="E405" s="1"/>
       <c r="F405" s="4"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>63</v>
       </c>
@@ -17709,7 +17709,7 @@
       <c r="E406" s="1"/>
       <c r="F406" s="4"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>62</v>
       </c>
@@ -17722,7 +17722,7 @@
       <c r="E407" s="1"/>
       <c r="F407" s="4"/>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>61</v>
       </c>
@@ -17735,7 +17735,7 @@
       <c r="E408" s="1"/>
       <c r="F408" s="4"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>60</v>
       </c>
@@ -17748,7 +17748,7 @@
       <c r="E409" s="1"/>
       <c r="F409" s="4"/>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>59</v>
       </c>
@@ -17761,7 +17761,7 @@
       <c r="E410" s="1"/>
       <c r="F410" s="4"/>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>58</v>
       </c>
@@ -17774,7 +17774,7 @@
       <c r="E411" s="1"/>
       <c r="F411" s="4"/>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>57</v>
       </c>
@@ -17787,7 +17787,7 @@
       <c r="E412" s="1"/>
       <c r="F412" s="4"/>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>56</v>
       </c>
@@ -17800,7 +17800,7 @@
       <c r="E413" s="1"/>
       <c r="F413" s="4"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>55</v>
       </c>
@@ -17813,7 +17813,7 @@
       <c r="E414" s="1"/>
       <c r="F414" s="4"/>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>54</v>
       </c>
@@ -17826,7 +17826,7 @@
       <c r="E415" s="1"/>
       <c r="F415" s="4"/>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>53</v>
       </c>
@@ -17839,7 +17839,7 @@
       <c r="E416" s="1"/>
       <c r="F416" s="4"/>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>52</v>
       </c>
@@ -17852,7 +17852,7 @@
       <c r="E417" s="1"/>
       <c r="F417" s="4"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>51</v>
       </c>
@@ -17865,7 +17865,7 @@
       <c r="E418" s="1"/>
       <c r="F418" s="4"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>50</v>
       </c>
@@ -17878,7 +17878,7 @@
       <c r="E419" s="1"/>
       <c r="F419" s="4"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>49</v>
       </c>
@@ -17891,7 +17891,7 @@
       <c r="E420" s="1"/>
       <c r="F420" s="4"/>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>48</v>
       </c>
@@ -17904,7 +17904,7 @@
       <c r="E421" s="1"/>
       <c r="F421" s="4"/>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>47</v>
       </c>
@@ -17917,7 +17917,7 @@
       <c r="E422" s="1"/>
       <c r="F422" s="4"/>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>46</v>
       </c>
@@ -17930,7 +17930,7 @@
       <c r="E423" s="1"/>
       <c r="F423" s="4"/>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>45</v>
       </c>
@@ -17943,7 +17943,7 @@
       <c r="E424" s="1"/>
       <c r="F424" s="4"/>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>44</v>
       </c>
@@ -17956,7 +17956,7 @@
       <c r="E425" s="1"/>
       <c r="F425" s="4"/>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>43</v>
       </c>
@@ -17969,7 +17969,7 @@
       <c r="E426" s="1"/>
       <c r="F426" s="4"/>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>42</v>
       </c>
@@ -17982,7 +17982,7 @@
       <c r="E427" s="1"/>
       <c r="F427" s="4"/>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>41</v>
       </c>
@@ -17995,7 +17995,7 @@
       <c r="E428" s="1"/>
       <c r="F428" s="4"/>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>40</v>
       </c>
@@ -18008,7 +18008,7 @@
       <c r="E429" s="1"/>
       <c r="F429" s="4"/>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>39</v>
       </c>
@@ -18021,7 +18021,7 @@
       <c r="E430" s="1"/>
       <c r="F430" s="4"/>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>38</v>
       </c>
@@ -18034,7 +18034,7 @@
       <c r="E431" s="1"/>
       <c r="F431" s="4"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>37</v>
       </c>
@@ -18047,7 +18047,7 @@
       <c r="E432" s="1"/>
       <c r="F432" s="4"/>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>36</v>
       </c>
@@ -18060,7 +18060,7 @@
       <c r="E433" s="1"/>
       <c r="F433" s="4"/>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>35</v>
       </c>
@@ -18073,7 +18073,7 @@
       <c r="E434" s="1"/>
       <c r="F434" s="4"/>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>34</v>
       </c>
@@ -18086,7 +18086,7 @@
       <c r="E435" s="1"/>
       <c r="F435" s="4"/>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>33</v>
       </c>
@@ -18099,7 +18099,7 @@
       <c r="E436" s="1"/>
       <c r="F436" s="4"/>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>32</v>
       </c>
@@ -18112,7 +18112,7 @@
       <c r="E437" s="1"/>
       <c r="F437" s="4"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>31</v>
       </c>
@@ -18125,7 +18125,7 @@
       <c r="E438" s="1"/>
       <c r="F438" s="4"/>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>30</v>
       </c>
@@ -18138,7 +18138,7 @@
       <c r="E439" s="1"/>
       <c r="F439" s="4"/>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>29</v>
       </c>
@@ -18151,7 +18151,7 @@
       <c r="E440" s="1"/>
       <c r="F440" s="4"/>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>28</v>
       </c>
@@ -18164,7 +18164,7 @@
       <c r="E441" s="1"/>
       <c r="F441" s="4"/>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>27</v>
       </c>
@@ -18177,7 +18177,7 @@
       <c r="E442" s="1"/>
       <c r="F442" s="4"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>26</v>
       </c>
@@ -18190,7 +18190,7 @@
       <c r="E443" s="1"/>
       <c r="F443" s="4"/>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>25</v>
       </c>
@@ -18203,7 +18203,7 @@
       <c r="E444" s="1"/>
       <c r="F444" s="4"/>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>24</v>
       </c>
@@ -18216,7 +18216,7 @@
       <c r="E445" s="1"/>
       <c r="F445" s="4"/>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>23</v>
       </c>
@@ -18229,7 +18229,7 @@
       <c r="E446" s="1"/>
       <c r="F446" s="4"/>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>22</v>
       </c>
@@ -18242,7 +18242,7 @@
       <c r="E447" s="1"/>
       <c r="F447" s="4"/>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>21</v>
       </c>
@@ -18255,7 +18255,7 @@
       <c r="E448" s="1"/>
       <c r="F448" s="4"/>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>20</v>
       </c>
@@ -18268,7 +18268,7 @@
       <c r="E449" s="1"/>
       <c r="F449" s="4"/>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>19</v>
       </c>
@@ -18281,7 +18281,7 @@
       <c r="E450" s="1"/>
       <c r="F450" s="4"/>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>18</v>
       </c>
@@ -18294,7 +18294,7 @@
       <c r="E451" s="1"/>
       <c r="F451" s="4"/>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>17</v>
       </c>
@@ -18307,7 +18307,7 @@
       <c r="E452" s="1"/>
       <c r="F452" s="4"/>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>16</v>
       </c>
@@ -18320,7 +18320,7 @@
       <c r="E453" s="1"/>
       <c r="F453" s="4"/>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>15</v>
       </c>
@@ -18333,7 +18333,7 @@
       <c r="E454" s="1"/>
       <c r="F454" s="4"/>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>14</v>
       </c>
@@ -18346,7 +18346,7 @@
       <c r="E455" s="1"/>
       <c r="F455" s="4"/>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>13</v>
       </c>
@@ -18359,7 +18359,7 @@
       <c r="E456" s="1"/>
       <c r="F456" s="4"/>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>12</v>
       </c>
@@ -18372,7 +18372,7 @@
       <c r="E457" s="1"/>
       <c r="F457" s="4"/>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>11</v>
       </c>
@@ -18385,7 +18385,7 @@
       <c r="E458" s="1"/>
       <c r="F458" s="4"/>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>10</v>
       </c>
@@ -18398,7 +18398,7 @@
       <c r="E459" s="1"/>
       <c r="F459" s="4"/>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>9</v>
       </c>
@@ -18411,7 +18411,7 @@
       <c r="E460" s="1"/>
       <c r="F460" s="4"/>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>8</v>
       </c>
@@ -18424,7 +18424,7 @@
       <c r="E461" s="1"/>
       <c r="F461" s="4"/>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>7</v>
       </c>
@@ -18437,7 +18437,7 @@
       <c r="E462" s="1"/>
       <c r="F462" s="4"/>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B463" s="1"/>
       <c r="C463" s="4"/>
     </row>
@@ -18453,7 +18453,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2562EC14-6E9A-4ABA-B8C8-40DA9B202ACA}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
